--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
@@ -938,19 +938,19 @@
     <t>215</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 4.595,49</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>28.9</t>
-  </si>
-  <si>
-    <t>5.37</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 4.569,26</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>28.7</t>
+  </si>
+  <si>
+    <t>5.40</t>
   </si>
   <si>
     <t>19.1</t>
@@ -959,13 +959,13 @@
     <t>7.1</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.2</t>
   </si>
   <si>
     <t>42.4%</t>
   </si>
   <si>
-    <t>17.2%</t>
+    <t>17.1%</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -989,16 +989,16 @@
     <t>3.0%</t>
   </si>
   <si>
-    <t>1105.0</t>
-  </si>
-  <si>
-    <t>905.0</t>
+    <t>1109.0</t>
+  </si>
+  <si>
+    <t>910.0</t>
   </si>
   <si>
     <t>76.0</t>
   </si>
   <si>
-    <t>12.0</t>
+    <t>13.0</t>
   </si>
   <si>
     <t>213.0</t>
@@ -1010,13 +1010,13 @@
     <t>22.0</t>
   </si>
   <si>
-    <t>347.0</t>
-  </si>
-  <si>
-    <t>157.0</t>
-  </si>
-  <si>
-    <t>210.0</t>
+    <t>348.0</t>
+  </si>
+  <si>
+    <t>158.0</t>
+  </si>
+  <si>
+    <t>212.0</t>
   </si>
   <si>
     <t>21.0</t>
@@ -7722,7 +7722,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7752,35 +7752,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>3382.6700000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>33</v>
+      </c>
+      <c r="O42" s="6">
+        <v>20</v>
+      </c>
+      <c r="P42" s="7">
+        <v>7.1333333333333337</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>20.344999999999999</v>
+      </c>
+      <c r="R42" s="8">
+        <v>5.788335</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -22383,7 +22441,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22413,35 +22471,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>2745.6999999999998</v>
+      </c>
+      <c r="N141" s="6">
+        <v>35</v>
+      </c>
+      <c r="O141" s="6">
+        <v>18</v>
+      </c>
+      <c r="P141" s="7">
+        <v>4.0562500000000004</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>16.557405555555555</v>
+      </c>
+      <c r="R141" s="8">
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -24969,7 +25085,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -24999,18 +25115,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>5358.4099999999999</v>
+      </c>
+      <c r="N159" s="6">
+        <v>48</v>
+      </c>
       <c r="O159" s="6">
         <v>33</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>5.1407808510638295</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>20.322727272727271</v>
+      </c>
+      <c r="R159" s="8">
+        <v>7.8388878787878777</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.21212121212121213</v>
+      </c>
       <c r="U159" s="9">
         <v>0.060606060606060608</v>
       </c>
@@ -32187,7 +32315,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -32217,35 +32345,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>2068.0599999999999</v>
+      </c>
+      <c r="N207" s="6">
+        <v>26</v>
+      </c>
+      <c r="O207" s="6">
+        <v>13</v>
+      </c>
+      <c r="P207" s="7">
+        <v>11.010869565217391</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>28.28717692307692</v>
+      </c>
+      <c r="R207" s="8">
+        <v>8.5371769230769239</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
@@ -938,25 +938,25 @@
     <t>215</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 4.569,26</t>
-  </si>
-  <si>
-    <t>48.4</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 4.563,05</t>
+  </si>
+  <si>
+    <t>48.3</t>
   </si>
   <si>
     <t>28.7</t>
   </si>
   <si>
-    <t>5.40</t>
-  </si>
-  <si>
-    <t>19.1</t>
-  </si>
-  <si>
-    <t>7.1</t>
+    <t>5.42</t>
+  </si>
+  <si>
+    <t>19.4</t>
+  </si>
+  <si>
+    <t>7.4</t>
   </si>
   <si>
     <t>6.2</t>
@@ -16686,7 +16686,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16716,14 +16716,26 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
+      <c r="M102" s="5">
+        <v>3421.3000000000002</v>
+      </c>
+      <c r="N102" s="6">
+        <v>33</v>
+      </c>
       <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
+      <c r="P102" s="7">
+        <v>8.6284935483870964</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>69.824304166666664</v>
+      </c>
+      <c r="R102" s="8">
+        <v>53.952779166666666</v>
+      </c>
       <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
+      <c r="T102" s="9">
+        <v>0</v>
+      </c>
       <c r="U102" s="9"/>
       <c r="V102" s="9"/>
       <c r="W102" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
@@ -938,19 +938,19 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
+    <t>28</t>
   </si>
   <si>
-    <t>R$ 4.563,05</t>
+    <t>R$ 4.558,86</t>
   </si>
   <si>
     <t>48.3</t>
   </si>
   <si>
-    <t>28.7</t>
+    <t>28.6</t>
   </si>
   <si>
-    <t>5.42</t>
+    <t>5.44</t>
   </si>
   <si>
     <t>19.4</t>
@@ -959,13 +959,13 @@
     <t>7.4</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.3</t>
   </si>
   <si>
-    <t>42.4%</t>
+    <t>42.1%</t>
   </si>
   <si>
-    <t>17.1%</t>
+    <t>17.4%</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -977,7 +977,7 @@
     <t>4.0%</t>
   </si>
   <si>
-    <t>1.1%</t>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -989,10 +989,13 @@
     <t>3.0%</t>
   </si>
   <si>
-    <t>1109.0</t>
+    <t>4.1%</t>
   </si>
   <si>
-    <t>910.0</t>
+    <t>1133.0</t>
+  </si>
+  <si>
+    <t>929.0</t>
   </si>
   <si>
     <t>76.0</t>
@@ -1001,25 +1004,22 @@
     <t>13.0</t>
   </si>
   <si>
-    <t>213.0</t>
+    <t>215.0</t>
   </si>
   <si>
-    <t>59.0</t>
+    <t>65.0</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>348.0</t>
+    <t>353.0</t>
   </si>
   <si>
     <t>158.0</t>
   </si>
   <si>
-    <t>212.0</t>
-  </si>
-  <si>
-    <t>21.0</t>
+    <t>222.0</t>
   </si>
   <si>
     <t>1</t>
@@ -14773,7 +14773,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14801,14 +14801,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>3782.4099999999999</v>
+      </c>
+      <c r="N89" s="6">
+        <v>41</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>9.0952999999999999</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>30.537500000000001</v>
+      </c>
+      <c r="R89" s="8">
+        <v>13.264581250000001</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -16722,7 +16734,9 @@
       <c r="N102" s="6">
         <v>33</v>
       </c>
-      <c r="O102" s="6"/>
+      <c r="O102" s="6">
+        <v>24</v>
+      </c>
       <c r="P102" s="7">
         <v>8.6284935483870964</v>
       </c>
@@ -16732,31 +16746,75 @@
       <c r="R102" s="8">
         <v>53.952779166666666</v>
       </c>
-      <c r="S102" s="8"/>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
       <c r="T102" s="9">
         <v>0</v>
       </c>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="U102" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -18686,33 +18744,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>19</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>6</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -29049,7 +29153,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31757,7 +31861,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33608,43 +33712,43 @@
         <v>325</v>
       </c>
       <c t="s" r="AC217" s="11">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c t="s" r="AD217" s="11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="AE217" s="11">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="AF217" s="11">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="AG217" s="11">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="AH217" s="11">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="AI217" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="AJ217" s="11">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="AK217" s="11">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="AL217" s="11">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="AM217" s="11">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="AN217" s="11">
         <v>323</v>
       </c>
       <c t="s" r="AO217" s="11">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AP217" s="12"/>
       <c t="s" r="AQ217" s="12">

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-13).xlsx
@@ -938,16 +938,16 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 4.558,86</t>
+    <t>R$ 4.523,46</t>
   </si>
   <si>
-    <t>48.3</t>
+    <t>47.9</t>
   </si>
   <si>
-    <t>28.6</t>
+    <t>28.7</t>
   </si>
   <si>
     <t>5.44</t>
@@ -956,16 +956,16 @@
     <t>19.4</t>
   </si>
   <si>
-    <t>7.4</t>
+    <t>7.3</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.5</t>
   </si>
   <si>
-    <t>42.1%</t>
+    <t>41.9%</t>
   </si>
   <si>
-    <t>17.4%</t>
+    <t>16.9%</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -974,7 +974,7 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>4.0%</t>
+    <t>3.9%</t>
   </si>
   <si>
     <t>1.2%</t>
@@ -983,22 +983,22 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>6.6%</t>
+    <t>6.4%</t>
   </si>
   <si>
-    <t>3.0%</t>
+    <t>2.9%</t>
   </si>
   <si>
-    <t>4.1%</t>
+    <t>4.0%</t>
   </si>
   <si>
-    <t>1133.0</t>
+    <t>1137.0</t>
   </si>
   <si>
-    <t>929.0</t>
+    <t>933.0</t>
   </si>
   <si>
-    <t>76.0</t>
+    <t>77.0</t>
   </si>
   <si>
     <t>13.0</t>
@@ -1013,10 +1013,10 @@
     <t>22.0</t>
   </si>
   <si>
-    <t>353.0</t>
+    <t>355.0</t>
   </si>
   <si>
-    <t>158.0</t>
+    <t>159.0</t>
   </si>
   <si>
     <t>222.0</t>
@@ -2206,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2236,35 +2236,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>8083.4399999999996</v>
+      </c>
+      <c r="N6" s="6">
+        <v>72</v>
+      </c>
+      <c r="O6" s="6">
+        <v>44</v>
+      </c>
+      <c r="P6" s="7">
+        <v>6.6711900000000002</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>15.773644186046512</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.469379069767442</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.53488372093023251</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9129,7 +9187,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9159,14 +9217,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>909.79999999999995</v>
+      </c>
+      <c r="N51" s="6">
+        <v>10</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>3.0016699999999998</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>26.033349999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>13.63335</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10198,33 +10268,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>42</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24121,7 +24237,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24151,35 +24267,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2586.1199999999999</v>
+      </c>
+      <c r="N151" s="6">
+        <v>34</v>
+      </c>
+      <c r="O151" s="6">
+        <v>29</v>
+      </c>
+      <c r="P151" s="7">
+        <v>6.2759794117647054</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>15.933334482758621</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.6890793103448276</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.48275862068965519</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25003,7 +25177,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25033,35 +25207,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>1445.96</v>
+      </c>
+      <c r="N157" s="6">
+        <v>22</v>
+      </c>
+      <c r="O157" s="6">
+        <v>14</v>
+      </c>
+      <c r="P157" s="7">
+        <v>6.257938095238095</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>16.010714285714286</v>
+      </c>
+      <c r="R157" s="8">
+        <v>2.7845214285714284</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25102,7 +25334,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25132,35 +25364,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>1757.2</v>
+      </c>
+      <c r="N158" s="6">
+        <v>17</v>
+      </c>
+      <c r="O158" s="6">
+        <v>13</v>
+      </c>
+      <c r="P158" s="7">
+        <v>5.7509823529411763</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>15.0359</v>
+      </c>
+      <c r="R158" s="8">
+        <v>2.2487153846153847</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26137,7 +26427,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26167,35 +26457,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>5774.6800000000003</v>
+      </c>
+      <c r="N165" s="6">
+        <v>58</v>
+      </c>
+      <c r="O165" s="6">
+        <v>41</v>
+      </c>
+      <c r="P165" s="7">
+        <v>5.2389875000000004</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>15.295121951219512</v>
+      </c>
+      <c r="R165" s="8">
+        <v>3.1723585365853659</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.36585365853658536</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
